--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.54832</v>
+        <v>16.85614</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1723</v>
+        <v>16.35314</v>
       </c>
       <c r="E2" t="n">
-        <v>16.64183</v>
+        <v>16.7343</v>
       </c>
       <c r="F2" t="n">
-        <v>42.07501</v>
+        <v>42.25341</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05069</v>
+        <v>0.05042</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79382</v>
+        <v>1.83062</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.813</v>
+        <v>16.76557</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57512</v>
+        <v>16.59253</v>
       </c>
       <c r="E3" t="n">
-        <v>16.25402</v>
+        <v>16.64677</v>
       </c>
       <c r="F3" t="n">
-        <v>42.57735</v>
+        <v>42.20716</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05035</v>
+        <v>0.05041</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8214</v>
+        <v>1.80195</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65518</v>
+        <v>16.55899</v>
       </c>
       <c r="D4" t="n">
-        <v>16.45439</v>
+        <v>16.39548</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58476</v>
+        <v>16.48299</v>
       </c>
       <c r="F4" t="n">
-        <v>42.11063</v>
+        <v>42.53683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04951</v>
+        <v>0.04929</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81136</v>
+        <v>1.80599</v>
       </c>
     </row>
   </sheetData>
